--- a/modules/weighting/docs/templates/Weight_Config.xlsx
+++ b/modules/weighting/docs/templates/Weight_Config.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="150">
   <si>
     <t xml:space="preserve">TURAS Weighting Module - Configuration</t>
   </si>
@@ -143,6 +143,9 @@
     <t xml:space="preserve">generate_stats_pack</t>
   </si>
   <si>
+    <t xml:space="preserve">Y</t>
+  </si>
+  <si>
     <t xml:space="preserve">Generate a diagnostic stats pack workbook alongside main output. The stats pack provides a full audit trail of data received, methods used, assumptions, and reproducibility — designed for advanced partners and research statisticians. Output file is named {output}_stats_pack.xlsx.</t>
   </si>
   <si>
@@ -260,7 +263,7 @@
     <t xml:space="preserve">[Optional] How to trim weights: cap (fixed multiplier of mean) or percentile (cap at Nth percentile).</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] Trimming threshold. For cap: max ratio (e.g. 5 = 5x mean). For percentile: percentile value (e.g. 95).</t>
+    <t xml:space="preserve">[Optional] Trimming threshold. For cap: max ratio (e.g. 5 = 5x mean). For percentile: a proportion strictly between 0 and 1 (e.g. 0.95 for the 95th percentile), NOT 95.</t>
   </si>
   <si>
     <t xml:space="preserve">wgt_demo</t>
@@ -272,9 +275,6 @@
     <t xml:space="preserve">Demographic rim weighting</t>
   </si>
   <si>
-    <t xml:space="preserve">Y</t>
-  </si>
-  <si>
     <t xml:space="preserve">cap</t>
   </si>
   <si>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">Advanced Weighting Settings</t>
   </si>
   <si>
-    <t xml:space="preserve">Optional per-weight overrides for iteration limits and convergence. Leave blank to use defaults.</t>
+    <t xml:space="preserve">Optional per-weight overrides for iteration limits, convergence and calibration method. Leave blank to use defaults.</t>
   </si>
   <si>
     <t xml:space="preserve">max_iterations</t>
@@ -413,7 +413,10 @@
     <t xml:space="preserve">convergence_tolerance</t>
   </si>
   <si>
-    <t xml:space="preserve">force_convergence</t>
+    <t xml:space="preserve">calibration_method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight_bounds</t>
   </si>
   <si>
     <t xml:space="preserve">[REQUIRED] Must match a weight_name from Weight_Specifications.</t>
@@ -422,10 +425,19 @@
     <t xml:space="preserve">[Optional] Maximum iterations for convergence (rim/rake methods). Default: 50.</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] Convergence threshold for rim/rake. Smaller = more precise but slower. Default: 0.001.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] If Y, use the last iteration result even if convergence was not achieved.</t>
+    <t xml:space="preserve">[Optional] Convergence threshold for rim/rake. Smaller = more precise but slower. Default: 0.0000001 (1e-7).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] How rim weights are fitted. Default: raking. Switch to logit when raking will not converge - a target needing a 3x+ stretch on one category often defeats raking at any bounds. logit needs FINITE weight_bounds on both sides. linear can produce zero or negative weights and is refused if it does.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Weight range enforced DURING calibration, as lower,upper (e.g. 0.3,3.0). Default: 0.3,3.0. Must be finite on both sides if calibration_method is logit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3,3.0</t>
   </si>
   <si>
     <t xml:space="preserve">Weighting Notes &amp; Documentation</t>
@@ -1169,13 +1181,13 @@
         <v>40</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>31</v>
@@ -1183,7 +1195,7 @@
     </row>
     <row r="16">
       <c r="A16" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -1192,41 +1204,41 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>14</v>
@@ -1235,15 +1247,15 @@
         <v>4</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>14</v>
@@ -1252,15 +1264,15 @@
         <v>4</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>14</v>
@@ -1269,15 +1281,15 @@
         <v>4</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -1286,7 +1298,7 @@
     </row>
     <row r="23">
       <c r="A23" s="15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>14</v>
@@ -1295,15 +1307,15 @@
         <v>4</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>14</v>
@@ -1312,15 +1324,15 @@
         <v>4</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>14</v>
@@ -1329,10 +1341,10 @@
         <v>4</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1387,66 +1399,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>85</v>
@@ -1486,13 +1498,13 @@
         <v>91</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>92</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>95</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="8">
@@ -1712,7 +1724,7 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>95</v>
@@ -2099,7 +2111,7 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>107</v>
@@ -2127,7 +2139,7 @@
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>114</v>
@@ -2141,7 +2153,7 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>114</v>
@@ -2155,7 +2167,7 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>117</v>
@@ -2169,7 +2181,7 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>117</v>
@@ -2183,7 +2195,7 @@
     </row>
     <row r="9">
       <c r="A9" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>117</v>
@@ -2834,7 +2846,7 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>114</v>
@@ -3227,6 +3239,7 @@
     <col min="2" max="2" width="18.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="22.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="20.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="18.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3241,7 +3254,7 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>129</v>
@@ -3252,33 +3265,42 @@
       <c r="D3" s="8" t="s">
         <v>131</v>
       </c>
+      <c r="E3" s="8" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>50</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>0.001</v>
+        <v>0.0000001</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>29</v>
+        <v>138</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="6">
@@ -3286,65 +3308,75 @@
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
     </row>
     <row r="7">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
     </row>
     <row r="8">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
     </row>
     <row r="9">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:B15">
@@ -3359,7 +3391,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"Y,N"</xm:f>
+            <xm:f>"raking,linear,logit"</xm:f>
           </x14:formula1>
           <xm:sqref>D5:D15</xm:sqref>
         </x14:dataValidation>
@@ -3380,44 +3412,44 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7">

--- a/modules/weighting/docs/templates/Weight_Config.xlsx
+++ b/modules/weighting/docs/templates/Weight_Config.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
   <si>
     <t xml:space="preserve">TURAS Weighting Module - Configuration</t>
   </si>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">[Optional] Human-readable description of what this weight corrects for.</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] Whether to cap extreme weights after calculation. Y or N.</t>
+    <t xml:space="preserve">[Optional] Whether to cap extreme weights AFTER calculation. Y or N. Design and cell weights only — a rim weight is refused, because capping afterwards breaks the margins raking just calibrated. For rim, use cap_weights in Advanced_Settings, which caps DURING calibration and keeps the margins.</t>
   </si>
   <si>
     <t xml:space="preserve">[Optional] How to trim weights: cap (fixed multiplier of mean) or percentile (cap at Nth percentile).</t>
@@ -273,9 +273,6 @@
   </si>
   <si>
     <t xml:space="preserve">Demographic rim weighting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cap</t>
   </si>
   <si>
     <t xml:space="preserve">wgt_design</t>
@@ -1458,24 +1455,24 @@
         <v>84</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="F5" s="17" t="n">
-        <v>5</v>
+        <v>14</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="C6" s="17" t="s">
         <v>87</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>88</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>29</v>
@@ -1489,19 +1486,19 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="C7" s="17" t="s">
         <v>90</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>91</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>41</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F7" s="17" t="n">
         <v>0.95</v>
@@ -1714,12 +1711,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3">
@@ -1727,38 +1724,38 @@
         <v>70</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>96</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="C4" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="D4" s="13" t="s">
         <v>100</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>102</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>103</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>45000</v>
@@ -1766,13 +1763,13 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>55000</v>
@@ -2101,12 +2098,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3">
@@ -2114,27 +2111,27 @@
         <v>70</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>108</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="C4" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="D4" s="13" t="s">
         <v>112</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="5">
@@ -2142,10 +2139,10 @@
         <v>82</v>
       </c>
       <c r="B5" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>114</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>115</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>48.5</v>
@@ -2156,10 +2153,10 @@
         <v>82</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>51.5</v>
@@ -2170,10 +2167,10 @@
         <v>82</v>
       </c>
       <c r="B7" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="17" t="s">
         <v>117</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>118</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>30</v>
@@ -2184,10 +2181,10 @@
         <v>82</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D8" s="17" t="n">
         <v>35</v>
@@ -2198,10 +2195,10 @@
         <v>82</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D9" s="17" t="n">
         <v>35</v>
@@ -2836,12 +2833,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
@@ -2849,38 +2846,38 @@
         <v>70</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="C4" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="D4" s="13" t="s">
         <v>125</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>15</v>
@@ -2888,13 +2885,13 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>17</v>
@@ -2902,13 +2899,13 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>16</v>
@@ -3244,12 +3241,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3">
@@ -3257,33 +3254,33 @@
         <v>70</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>131</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="C4" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="D4" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="E4" s="13" t="s">
         <v>136</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="5">
@@ -3297,10 +3294,10 @@
         <v>0.0000001</v>
       </c>
       <c r="D5" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>138</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="6">
@@ -3412,44 +3409,44 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>142</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>144</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>146</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>148</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="7">

--- a/modules/weighting/docs/templates/Weight_Config.xlsx
+++ b/modules/weighting/docs/templates/Weight_Config.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
   <si>
     <t xml:space="preserve">TURAS Weighting Module - Configuration</t>
   </si>
@@ -416,6 +416,9 @@
     <t xml:space="preserve">weight_bounds</t>
   </si>
   <si>
+    <t xml:space="preserve">margin_tolerance</t>
+  </si>
+  <si>
     <t xml:space="preserve">[REQUIRED] Must match a weight_name from Weight_Specifications.</t>
   </si>
   <si>
@@ -429,6 +432,9 @@
   </si>
   <si>
     <t xml:space="preserve">[Optional] Weight range enforced DURING calibration, as lower,upper (e.g. 0.3,3.0). Default: 0.3,3.0. Must be finite on both sides if calibration_method is logit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] How far a weighted margin may sit from its target, in percentage points, before the run stops calling itself converged and reports PARTIAL naming the categories that missed. Default: 0.5. Raise it only if you accept the gap - it changes what the run reports, not what the weights are.</t>
   </si>
   <si>
     <t xml:space="preserve">raking</t>
@@ -3237,6 +3243,7 @@
     <col min="3" max="3" width="22.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="20.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="18.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3265,22 +3272,28 @@
       <c r="E3" s="8" t="s">
         <v>131</v>
       </c>
+      <c r="F3" s="8" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="5">
@@ -3294,10 +3307,13 @@
         <v>0.0000001</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>138</v>
+        <v>140</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -3306,6 +3322,7 @@
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
     </row>
     <row r="7">
       <c r="A7" s="11"/>
@@ -3313,6 +3330,7 @@
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
     </row>
     <row r="8">
       <c r="A8" s="11"/>
@@ -3320,6 +3338,7 @@
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
     </row>
     <row r="9">
       <c r="A9" s="11"/>
@@ -3327,6 +3346,7 @@
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
@@ -3334,6 +3354,7 @@
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
@@ -3341,6 +3362,7 @@
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
@@ -3348,6 +3370,7 @@
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
@@ -3355,6 +3378,7 @@
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
@@ -3362,6 +3386,7 @@
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
@@ -3369,11 +3394,12 @@
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:B15">
@@ -3409,44 +3435,44 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7">

--- a/modules/weighting/docs/templates/Weight_Config.xlsx
+++ b/modules/weighting/docs/templates/Weight_Config.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
   <si>
     <t xml:space="preserve">TURAS Weighting Module - Configuration</t>
   </si>
@@ -419,6 +419,9 @@
     <t xml:space="preserve">margin_tolerance</t>
   </si>
   <si>
+    <t xml:space="preserve">allow_unmatched</t>
+  </si>
+  <si>
     <t xml:space="preserve">[REQUIRED] Must match a weight_name from Weight_Specifications.</t>
   </si>
   <si>
@@ -435,6 +438,9 @@
   </si>
   <si>
     <t xml:space="preserve">[Optional] How far a weighted margin may sit from its target, in percentage points, before the run stops calling itself converged and reports PARTIAL naming the categories that missed. Default: 0.5. Raise it only if you accept the gap - it changes what the run reports, not what the weights are.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Y or N. Default N. Design and cell weights refuse when any respondent would end up with no weight - an unmatched category, a missing value in a weighting variable, or a target cell nobody is in. Set Y only if you have decided those respondents should be left out; their weights stay blank and the count is reported.</t>
   </si>
   <si>
     <t xml:space="preserve">raking</t>
@@ -3244,6 +3250,7 @@
     <col min="4" max="4" width="20.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="18.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="18.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3275,25 +3282,31 @@
       <c r="F3" s="8" t="s">
         <v>132</v>
       </c>
+      <c r="G3" s="8" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="5">
@@ -3307,13 +3320,16 @@
         <v>0.0000001</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>0.5</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -3323,6 +3339,7 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7">
       <c r="A7" s="11"/>
@@ -3331,6 +3348,7 @@
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
     </row>
     <row r="8">
       <c r="A8" s="11"/>
@@ -3339,6 +3357,7 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
     </row>
     <row r="9">
       <c r="A9" s="11"/>
@@ -3347,6 +3366,7 @@
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
@@ -3355,6 +3375,7 @@
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
@@ -3363,6 +3384,7 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
@@ -3371,6 +3393,7 @@
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
@@ -3379,6 +3402,7 @@
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
@@ -3387,6 +3411,7 @@
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
@@ -3395,11 +3420,12 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:B15">
@@ -3435,44 +3461,44 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7">

--- a/modules/weighting/docs/templates/Weight_Config.xlsx
+++ b/modules/weighting/docs/templates/Weight_Config.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
   <si>
     <t xml:space="preserve">TURAS Weighting Module - Configuration</t>
   </si>
@@ -422,6 +422,9 @@
     <t xml:space="preserve">allow_unmatched</t>
   </si>
   <si>
+    <t xml:space="preserve">grossing</t>
+  </si>
+  <si>
     <t xml:space="preserve">[REQUIRED] Must match a weight_name from Weight_Specifications.</t>
   </si>
   <si>
@@ -441,6 +444,9 @@
   </si>
   <si>
     <t xml:space="preserve">[Optional] Y or N. Default N. Design and cell weights refuse when any respondent would end up with no weight - an unmatched category, a missing value in a weighting variable, or a target cell nobody is in. Set Y only if you have decided those respondents should be left out; their weights stay blank and the count is reported.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Design weights only. Y or N, default N. Design weights are population/sample, so they naturally arrive at population scale. N normalises them to sum to the sample size, matching rim weights, so two weights on one study cannot put weighted bases orders of magnitude apart. Y keeps population scale for grossed-up counts. Kish n_eff is scale-invariant either way, so significance testing is unaffected - what changes is every weighted N on the report.</t>
   </si>
   <si>
     <t xml:space="preserve">raking</t>
@@ -3251,6 +3257,7 @@
     <col min="5" max="5" width="18.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="18.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="14.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3285,28 +3292,34 @@
       <c r="G3" s="8" t="s">
         <v>133</v>
       </c>
+      <c r="H3" s="8" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="5">
@@ -3320,15 +3333,18 @@
         <v>0.0000001</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="G5" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="17" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3340,6 +3356,7 @@
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
     </row>
     <row r="7">
       <c r="A7" s="11"/>
@@ -3349,6 +3366,7 @@
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
     </row>
     <row r="8">
       <c r="A8" s="11"/>
@@ -3358,6 +3376,7 @@
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
     </row>
     <row r="9">
       <c r="A9" s="11"/>
@@ -3367,6 +3386,7 @@
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
@@ -3376,6 +3396,7 @@
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
@@ -3385,6 +3406,7 @@
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
@@ -3394,6 +3416,7 @@
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
@@ -3403,6 +3426,7 @@
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
@@ -3412,6 +3436,7 @@
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
@@ -3421,11 +3446,12 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:B15">
@@ -3461,44 +3487,44 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7">

--- a/modules/weighting/docs/templates/Weight_Config.xlsx
+++ b/modules/weighting/docs/templates/Weight_Config.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
   <si>
     <t xml:space="preserve">TURAS Weighting Module - Configuration</t>
   </si>
@@ -422,6 +422,9 @@
     <t xml:space="preserve">allow_unmatched</t>
   </si>
   <si>
+    <t xml:space="preserve">allow_empty_targets</t>
+  </si>
+  <si>
     <t xml:space="preserve">grossing</t>
   </si>
   <si>
@@ -443,7 +446,10 @@
     <t xml:space="preserve">[Optional] How far a weighted margin may sit from its target, in percentage points, before the run stops calling itself converged and reports PARTIAL naming the categories that missed. Default: 0.5. Raise it only if you accept the gap - it changes what the run reports, not what the weights are.</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] Y or N. Default N. Design and cell weights refuse when any respondent would end up with no weight - an unmatched category, a missing value in a weighting variable, or a target cell nobody is in. Set Y only if you have decided those respondents should be left out; their weights stay blank and the count is reported.</t>
+    <t xml:space="preserve">[Optional] Y or N. Default N. Design and cell weights refuse when any RESPONDENT would end up with no weight - an unmatched category, a missing value in a weighting variable, or a cell whose target is zero. Set Y only if you have decided those respondents should be left out; their weights stay blank, the count is reported, and the remaining weights sum to the respondents who kept one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Y or N. Default N. The mirror image of allow_unmatched: design and cell weights refuse when a TARGET has a population share but nobody in the sample to carry it. Set Y to proceed - the orphaned share is redistributed across the targets that do have respondents, so the weighted base is not short, and the console says how much moved. Those respondents are then standing in for people the sample never reached, which must be stated wherever the numbers are quoted.</t>
   </si>
   <si>
     <t xml:space="preserve">[Optional] Design weights only. Y or N, default N. Design weights are population/sample, so they naturally arrive at population scale. N normalises them to sum to the sample size, matching rim weights, so two weights on one study cannot put weighted bases orders of magnitude apart. Y keeps population scale for grossed-up counts. Kish n_eff is scale-invariant either way, so significance testing is unaffected - what changes is every weighted N on the report.</t>
@@ -3257,7 +3263,8 @@
     <col min="5" max="5" width="18.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="18.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="14.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="20.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="14.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3295,31 +3302,37 @@
       <c r="H3" s="8" t="s">
         <v>134</v>
       </c>
+      <c r="I3" s="8" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="5">
@@ -3333,10 +3346,10 @@
         <v>0.0000001</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>0.5</v>
@@ -3345,6 +3358,9 @@
         <v>29</v>
       </c>
       <c r="H5" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="17" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3357,6 +3373,7 @@
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
     </row>
     <row r="7">
       <c r="A7" s="11"/>
@@ -3367,6 +3384,7 @@
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
     </row>
     <row r="8">
       <c r="A8" s="11"/>
@@ -3377,6 +3395,7 @@
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
     </row>
     <row r="9">
       <c r="A9" s="11"/>
@@ -3387,6 +3406,7 @@
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
@@ -3397,6 +3417,7 @@
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
@@ -3407,6 +3428,7 @@
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
@@ -3417,6 +3439,7 @@
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
@@ -3427,6 +3450,7 @@
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
@@ -3437,6 +3461,7 @@
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
@@ -3447,11 +3472,12 @@
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:B15">
@@ -3487,44 +3513,44 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7">
